--- a/data/Reports.xlsx
+++ b/data/Reports.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\landscapingUOB-api\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4040E60-FB46-4A21-AD30-E103931C8A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F78EA7BE-A907-48F0-B81A-15CD6BBE5EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="271">
   <si>
     <t>Year</t>
   </si>
@@ -724,27 +724,12 @@
     <t>College of Teachers S22</t>
   </si>
   <si>
-    <t>Main Streets to Western Gate</t>
-  </si>
-  <si>
-    <t>College of Applied Sciences and S20A</t>
-  </si>
-  <si>
     <t>S20 Roundabout Leading to Eastern Gate</t>
   </si>
   <si>
-    <t>Agricultural Area to the Right of Administration Hall Exit and Surroundings</t>
-  </si>
-  <si>
-    <t>In Front of College of IT S40</t>
-  </si>
-  <si>
     <t>In Front of Health Clinic Building</t>
   </si>
   <si>
-    <t>S39A</t>
-  </si>
-  <si>
     <t>Street Leading to College of Science Roundabout</t>
   </si>
   <si>
@@ -794,6 +779,60 @@
   </si>
   <si>
     <t>https://maps.app.goo.gl/TPjgki8dog5mWmFv5</t>
+  </si>
+  <si>
+    <t>Agricultural Area to the Right of the Basement Exit and Surroundings</t>
+  </si>
+  <si>
+    <t>In Front of the College of IT (S40)</t>
+  </si>
+  <si>
+    <t>Behind the Mosque Adjacent to Hall S6</t>
+  </si>
+  <si>
+    <t>In Front of Building S37</t>
+  </si>
+  <si>
+    <t>Rest Areas Behind the College of Science</t>
+  </si>
+  <si>
+    <t>Behind the College of Engineering (S17)</t>
+  </si>
+  <si>
+    <t>Hills Near the Eastern Gate with the Triangular Basin in Front</t>
+  </si>
+  <si>
+    <t>Physical Education Department (S20A)</t>
+  </si>
+  <si>
+    <t>Main Streets Leading to the Western Gate</t>
+  </si>
+  <si>
+    <t>In Front of S20</t>
+  </si>
+  <si>
+    <t>College of Applied Sciences (S20B, S20C)</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/JyySVn31dhgevcwD7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/pxD22Yf1izzmhLX57</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/vET6QU7PCBxRYSSdA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/ootz4yWCEa1i37Zt9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/rVv47kpNh2fyQHuc8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/wDx5RxLN1KAw4PPZ6</t>
+  </si>
+  <si>
+    <t>S39A Building</t>
   </si>
 </sst>
 </file>
@@ -830,7 +869,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -867,6 +906,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -896,7 +941,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -947,6 +992,30 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1251,12 +1320,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" style="17" customWidth="1"/>
     <col min="2" max="2" width="12" style="17" customWidth="1"/>
-    <col min="3" max="3" width="35" style="18" customWidth="1"/>
+    <col min="3" max="3" width="37" style="18" customWidth="1"/>
     <col min="4" max="4" width="45" style="18" customWidth="1"/>
     <col min="5" max="5" width="40" style="18" customWidth="1"/>
     <col min="6" max="6" width="12" style="18" customWidth="1"/>
@@ -1312,7 +1381,7 @@
       <c r="C2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="26" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="4" t="s">
@@ -1347,7 +1416,7 @@
       <c r="C3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="26" t="s">
         <v>19</v>
       </c>
       <c r="E3" s="4" t="s">
@@ -1382,7 +1451,7 @@
       <c r="C4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="26" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="4" t="s">
@@ -1417,7 +1486,7 @@
       <c r="C5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="26" t="s">
         <v>33</v>
       </c>
       <c r="E5" s="4" t="s">
@@ -1452,7 +1521,7 @@
       <c r="C6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="26" t="s">
         <v>39</v>
       </c>
       <c r="E6" s="4" t="s">
@@ -1487,7 +1556,7 @@
       <c r="C7" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="26" t="s">
         <v>47</v>
       </c>
       <c r="E7" s="4" t="s">
@@ -1522,7 +1591,7 @@
       <c r="C8" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="26" t="s">
         <v>54</v>
       </c>
       <c r="E8" s="4" t="s">
@@ -1557,7 +1626,7 @@
       <c r="C9" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="26" t="s">
         <v>61</v>
       </c>
       <c r="E9" s="4" t="s">
@@ -1592,7 +1661,7 @@
       <c r="C10" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="26" t="s">
         <v>67</v>
       </c>
       <c r="E10" s="4" t="s">
@@ -1627,7 +1696,7 @@
       <c r="C11" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="26" t="s">
         <v>73</v>
       </c>
       <c r="E11" s="4" t="s">
@@ -1662,7 +1731,7 @@
       <c r="C12" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="26" t="s">
         <v>80</v>
       </c>
       <c r="E12" s="4" t="s">
@@ -1697,7 +1766,7 @@
       <c r="C13" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="26" t="s">
         <v>87</v>
       </c>
       <c r="E13" s="4" t="s">
@@ -1732,7 +1801,7 @@
       <c r="C14" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="26" t="s">
         <v>95</v>
       </c>
       <c r="E14" s="4" t="s">
@@ -1767,7 +1836,7 @@
       <c r="C15" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="26" t="s">
         <v>102</v>
       </c>
       <c r="E15" s="4" t="s">
@@ -1802,7 +1871,7 @@
       <c r="C16" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="26" t="s">
         <v>107</v>
       </c>
       <c r="E16" s="4" t="s">
@@ -1837,7 +1906,7 @@
       <c r="C17" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="26" t="s">
         <v>114</v>
       </c>
       <c r="E17" s="4" t="s">
@@ -1872,7 +1941,7 @@
       <c r="C18" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="26" t="s">
         <v>121</v>
       </c>
       <c r="E18" s="4" t="s">
@@ -1907,7 +1976,7 @@
       <c r="C19" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="26" t="s">
         <v>126</v>
       </c>
       <c r="E19" s="4" t="s">
@@ -1942,7 +2011,7 @@
       <c r="C20" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="26" t="s">
         <v>133</v>
       </c>
       <c r="E20" s="4" t="s">
@@ -1977,7 +2046,7 @@
       <c r="C21" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="26" t="s">
         <v>139</v>
       </c>
       <c r="E21" s="4" t="s">
@@ -2012,7 +2081,7 @@
       <c r="C22" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="26" t="s">
         <v>145</v>
       </c>
       <c r="E22" s="4" t="s">
@@ -2047,7 +2116,7 @@
       <c r="C23" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="26" t="s">
         <v>149</v>
       </c>
       <c r="E23" s="4" t="s">
@@ -2082,7 +2151,7 @@
       <c r="C24" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="26" t="s">
         <v>153</v>
       </c>
       <c r="E24" s="4" t="s">
@@ -2117,7 +2186,7 @@
       <c r="C25" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="25" t="s">
         <v>159</v>
       </c>
       <c r="E25" s="7" t="s">
@@ -2152,7 +2221,7 @@
       <c r="C26" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="25" t="s">
         <v>166</v>
       </c>
       <c r="E26" s="7" t="s">
@@ -2187,7 +2256,7 @@
       <c r="C27" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="25" t="s">
         <v>173</v>
       </c>
       <c r="E27" s="7" t="s">
@@ -2222,7 +2291,7 @@
       <c r="C28" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="25" t="s">
         <v>180</v>
       </c>
       <c r="E28" s="7" t="s">
@@ -2257,7 +2326,7 @@
       <c r="C29" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="25" t="s">
         <v>186</v>
       </c>
       <c r="E29" s="7" t="s">
@@ -2292,7 +2361,7 @@
       <c r="C30" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="25" t="s">
         <v>193</v>
       </c>
       <c r="E30" s="7" t="s">
@@ -2327,7 +2396,7 @@
       <c r="C31" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="25" t="s">
         <v>199</v>
       </c>
       <c r="E31" s="7" t="s">
@@ -2362,7 +2431,7 @@
       <c r="C32" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="25" t="s">
         <v>206</v>
       </c>
       <c r="E32" s="7" t="s">
@@ -2397,7 +2466,7 @@
       <c r="C33" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="25" t="s">
         <v>212</v>
       </c>
       <c r="E33" s="7" t="s">
@@ -2432,7 +2501,7 @@
       <c r="C34" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="25" t="s">
         <v>217</v>
       </c>
       <c r="E34" s="7" t="s">
@@ -2467,7 +2536,7 @@
       <c r="C35" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="25" t="s">
         <v>224</v>
       </c>
       <c r="E35" s="7" t="s">
@@ -2503,7 +2572,7 @@
         <v>228</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="E36" s="10"/>
     </row>
@@ -2518,7 +2587,7 @@
         <v>229</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E37" s="10"/>
     </row>
@@ -2533,7 +2602,7 @@
         <v>230</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E38" s="10"/>
     </row>
@@ -2545,29 +2614,29 @@
         <v>4</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E39" s="10"/>
     </row>
-    <row r="40" spans="1:11" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A40" s="9">
+    <row r="40" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="13">
         <v>2026</v>
       </c>
       <c r="B40" s="9">
         <v>5</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="E40" s="10"/>
-    </row>
-    <row r="41" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C40" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="E40" s="14"/>
+    </row>
+    <row r="41" spans="1:11" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A41" s="9">
         <v>2026</v>
       </c>
@@ -2575,10 +2644,10 @@
         <v>6</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E41" s="10"/>
     </row>
@@ -2590,10 +2659,10 @@
         <v>7</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E42" s="10"/>
     </row>
@@ -2604,136 +2673,270 @@
       <c r="B43" s="9">
         <v>8</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="D43" s="11" t="s">
-        <v>250</v>
+      <c r="C43" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D43" s="23" t="s">
+        <v>264</v>
       </c>
       <c r="E43" s="10"/>
     </row>
-    <row r="44" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="13">
+    <row r="44" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="9">
         <v>2026</v>
       </c>
-      <c r="B44" s="13">
+      <c r="B44" s="9">
         <v>9</v>
       </c>
-      <c r="C44" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>251</v>
-      </c>
-      <c r="E44" s="14"/>
-    </row>
-    <row r="45" spans="1:11" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="C44" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="D44" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="E44" s="10"/>
+    </row>
+    <row r="45" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9">
         <v>2026</v>
       </c>
       <c r="B45" s="9">
         <v>10</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="D45" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="E45" s="10"/>
+    </row>
+    <row r="46" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="19">
+        <v>2027</v>
+      </c>
+      <c r="B46" s="19">
+        <v>1</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="D46" s="21" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" s="22" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A47" s="19">
+        <v>2027</v>
+      </c>
+      <c r="B47" s="19">
+        <v>2</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="D47" s="21" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="19">
+        <v>2027</v>
+      </c>
+      <c r="B48" s="19">
+        <v>3</v>
+      </c>
+      <c r="C48" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="D48" s="21" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="19">
+        <v>2027</v>
+      </c>
+      <c r="B49" s="19">
+        <v>4</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="D49" s="21" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="19">
+        <v>2027</v>
+      </c>
+      <c r="B50" s="19">
+        <v>5</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="D50" s="21" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="19">
+        <v>2027</v>
+      </c>
+      <c r="B51" s="19">
+        <v>6</v>
+      </c>
+      <c r="C51" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" s="22" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A52" s="19">
+        <v>2027</v>
+      </c>
+      <c r="B52" s="19">
+        <v>7</v>
+      </c>
+      <c r="C52" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="D52" s="21" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="19">
+        <v>2027</v>
+      </c>
+      <c r="B53" s="19">
+        <v>8</v>
+      </c>
+      <c r="C53" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D53" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="E45" s="10"/>
-    </row>
-    <row r="46" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B46" s="9">
+    </row>
+    <row r="54" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="19">
+        <v>2027</v>
+      </c>
+      <c r="B54" s="19">
+        <v>9</v>
+      </c>
+      <c r="C54" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="D54" s="24" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="19">
+        <v>2027</v>
+      </c>
+      <c r="B55" s="19">
+        <v>10</v>
+      </c>
+      <c r="C55" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="D55" s="24" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" s="22" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A56" s="19">
+        <v>2027</v>
+      </c>
+      <c r="B56" s="19">
         <v>11</v>
       </c>
-      <c r="C46" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="E46" s="10"/>
-    </row>
-    <row r="47" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B47" s="9">
+      <c r="C56" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="D56" s="24" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="19">
+        <v>2027</v>
+      </c>
+      <c r="B57" s="19">
         <v>12</v>
       </c>
-      <c r="C47" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="E47" s="10"/>
-    </row>
-    <row r="48" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B48" s="9">
-        <v>13</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="E48" s="10"/>
-    </row>
-    <row r="49" spans="1:5" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A49" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B49" s="9">
-        <v>14</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="E49" s="10"/>
-    </row>
-    <row r="50" spans="1:5" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B50" s="9">
-        <v>15</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="E50" s="10"/>
+      <c r="C57" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="D57" s="24" t="s">
+        <v>269</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D36" r:id="rId1" xr:uid="{1000462C-B238-431A-B2A1-3FC2BD2E2813}"/>
     <hyperlink ref="D37" r:id="rId2" xr:uid="{1B9305A2-EFAE-494D-AE61-72B82236A00A}"/>
     <hyperlink ref="D38" r:id="rId3" xr:uid="{37366389-41FF-4E4B-BBAA-23F6E2BDE2E5}"/>
-    <hyperlink ref="D39" r:id="rId4" xr:uid="{005A1CEE-5E9C-41CE-ADDB-E229F3A1DF65}"/>
-    <hyperlink ref="D40" r:id="rId5" xr:uid="{0D35B99D-C761-48D2-A6FC-1AA9DABC570E}"/>
-    <hyperlink ref="D41" r:id="rId6" xr:uid="{2C3EF60F-AF56-486A-A65A-90521D1BE076}"/>
-    <hyperlink ref="D42" r:id="rId7" xr:uid="{C95DBB32-C8B9-4192-B5A8-A2BBC5AE8709}"/>
-    <hyperlink ref="D43" r:id="rId8" xr:uid="{0245B09C-A05C-42F8-9F53-B3C0DF8A3B3B}"/>
-    <hyperlink ref="D44" r:id="rId9" xr:uid="{41838A62-16DE-40C3-A6D6-65FCB68C828C}"/>
-    <hyperlink ref="D45" r:id="rId10" xr:uid="{1DA3C22A-9C35-431D-9E54-09A3B7395A7F}"/>
-    <hyperlink ref="D46" r:id="rId11" xr:uid="{D058C4E8-F8D4-42F8-A17C-BC9F6C69C57E}"/>
-    <hyperlink ref="D47" r:id="rId12" xr:uid="{D2DB956F-0AE2-4C2E-8230-86EBD2EFD849}"/>
-    <hyperlink ref="D48" r:id="rId13" xr:uid="{7FDA2993-EE4C-4AEE-A744-BD17EE8DF685}"/>
-    <hyperlink ref="D49" r:id="rId14" xr:uid="{C3597594-CEFA-42FD-809C-D15002498BB3}"/>
-    <hyperlink ref="D50" r:id="rId15" xr:uid="{D97DA6E9-7A4E-4C31-A094-581BEFAE38C5}"/>
+    <hyperlink ref="D47" r:id="rId4" xr:uid="{0D35B99D-C761-48D2-A6FC-1AA9DABC570E}"/>
+    <hyperlink ref="D48" r:id="rId5" xr:uid="{2C3EF60F-AF56-486A-A65A-90521D1BE076}"/>
+    <hyperlink ref="D39" r:id="rId6" xr:uid="{C95DBB32-C8B9-4192-B5A8-A2BBC5AE8709}"/>
+    <hyperlink ref="D49" r:id="rId7" xr:uid="{0245B09C-A05C-42F8-9F53-B3C0DF8A3B3B}"/>
+    <hyperlink ref="D40" r:id="rId8" xr:uid="{41838A62-16DE-40C3-A6D6-65FCB68C828C}"/>
+    <hyperlink ref="D41" r:id="rId9" xr:uid="{1DA3C22A-9C35-431D-9E54-09A3B7395A7F}"/>
+    <hyperlink ref="D42" r:id="rId10" xr:uid="{D058C4E8-F8D4-42F8-A17C-BC9F6C69C57E}"/>
+    <hyperlink ref="D50" r:id="rId11" xr:uid="{D2DB956F-0AE2-4C2E-8230-86EBD2EFD849}"/>
+    <hyperlink ref="D51" r:id="rId12" xr:uid="{7FDA2993-EE4C-4AEE-A744-BD17EE8DF685}"/>
+    <hyperlink ref="D52" r:id="rId13" xr:uid="{C3597594-CEFA-42FD-809C-D15002498BB3}"/>
+    <hyperlink ref="D53" r:id="rId14" xr:uid="{D97DA6E9-7A4E-4C31-A094-581BEFAE38C5}"/>
+    <hyperlink ref="D46" r:id="rId15" xr:uid="{66A90A50-7813-4BE2-835B-908012476FD3}"/>
+    <hyperlink ref="D43" r:id="rId16" xr:uid="{147ACBB0-7330-4375-A5F5-59953D8672C7}"/>
+    <hyperlink ref="D54" r:id="rId17" xr:uid="{BFA2C4D2-299F-48F3-8C92-FA17876C33A6}"/>
+    <hyperlink ref="D44" r:id="rId18" xr:uid="{89B226A2-CD02-441A-9332-0B81D06E4B1B}"/>
+    <hyperlink ref="D55" r:id="rId19" xr:uid="{0455FD2A-FBB6-4033-952F-93501D724B92}"/>
+    <hyperlink ref="D56" r:id="rId20" xr:uid="{6900060F-FF2A-4358-B515-6B63FC613431}"/>
+    <hyperlink ref="D57" r:id="rId21" xr:uid="{57F6A3F4-C756-45F7-BF88-FF8069986A7A}"/>
+    <hyperlink ref="D35" r:id="rId22" xr:uid="{D5D38438-E4B6-481E-8C69-DFDC27DE2CD2}"/>
+    <hyperlink ref="D45" r:id="rId23" xr:uid="{A775D76D-67D0-401B-BFFA-3EBAA24D153A}"/>
+    <hyperlink ref="D34" r:id="rId24" xr:uid="{A2DE1ABB-0FFA-4088-A49E-6A441A99A49F}"/>
+    <hyperlink ref="D33" r:id="rId25" xr:uid="{6F02F8FA-F7B3-4BA7-8A9D-E1158CE77C4F}"/>
+    <hyperlink ref="D2" r:id="rId26" xr:uid="{79CA4E29-85C4-4AD4-AE93-29AE46A02F70}"/>
+    <hyperlink ref="D3" r:id="rId27" xr:uid="{8FE052BA-6187-4AF2-96B5-E2BDC354F301}"/>
+    <hyperlink ref="D4" r:id="rId28" xr:uid="{A671D8F8-7D8B-441C-B77D-0B0B4D441A75}"/>
+    <hyperlink ref="D5" r:id="rId29" xr:uid="{0E6A5934-10C2-4980-81FD-2F67B4163433}"/>
+    <hyperlink ref="D6" r:id="rId30" xr:uid="{A9A35661-FA2C-4DC1-BE07-8625BA1F0B5F}"/>
+    <hyperlink ref="D7" r:id="rId31" xr:uid="{DA461EBA-4A61-477C-B744-D7C99F95BBF7}"/>
+    <hyperlink ref="D8" r:id="rId32" xr:uid="{C43799FD-F25C-42F7-BDFA-BF791BD540EA}"/>
+    <hyperlink ref="D9" r:id="rId33" xr:uid="{5A78ADC0-925A-42A4-A592-568FA7C436FB}"/>
+    <hyperlink ref="D10" r:id="rId34" xr:uid="{0944D076-16F5-4B91-9488-413CEA4A6980}"/>
+    <hyperlink ref="D11" r:id="rId35" xr:uid="{C38C17D8-DBF0-48C6-A2CA-DC28FD01BEB2}"/>
+    <hyperlink ref="D12" r:id="rId36" xr:uid="{D4CC19BE-B190-4A1C-9DA0-01FAA4EDBCAF}"/>
+    <hyperlink ref="D13" r:id="rId37" xr:uid="{4331AB42-39FF-4051-932A-89EFB36301DD}"/>
+    <hyperlink ref="D14" r:id="rId38" xr:uid="{81F82AAB-5CA8-4152-B8FF-AA0C2DE08EF5}"/>
+    <hyperlink ref="D15" r:id="rId39" xr:uid="{7BD99EA3-927D-43E9-9AC7-A70A5684D556}"/>
+    <hyperlink ref="D16" r:id="rId40" xr:uid="{107FB13C-7F5A-4ADD-990A-96A92DC01BA9}"/>
+    <hyperlink ref="D17" r:id="rId41" xr:uid="{E736C218-392A-4B75-A773-B7D7A5EC652F}"/>
+    <hyperlink ref="D18" r:id="rId42" xr:uid="{ABB99BE6-7A82-452B-A63F-9889DAB6A774}"/>
+    <hyperlink ref="D19" r:id="rId43" xr:uid="{8EB35F16-A8D0-4F42-AE0A-4D6D1C9EC389}"/>
+    <hyperlink ref="D20" r:id="rId44" xr:uid="{719FA258-8EAA-4740-B885-2B5CC8DB7666}"/>
+    <hyperlink ref="D21" r:id="rId45" xr:uid="{295BC305-8AD9-4C0E-8CD4-0A19B553A772}"/>
+    <hyperlink ref="D22" r:id="rId46" xr:uid="{47925947-372F-4387-87D3-939AC55D6B43}"/>
+    <hyperlink ref="D23" r:id="rId47" xr:uid="{F379549D-1131-43D7-95DF-79980D36864C}"/>
+    <hyperlink ref="D24" r:id="rId48" xr:uid="{97E1EFEC-C0D3-4FEA-8629-B84C1D42D812}"/>
+    <hyperlink ref="D25" r:id="rId49" xr:uid="{B0CE3390-CA48-4032-86F9-99C54FF5E06D}"/>
+    <hyperlink ref="D26" r:id="rId50" xr:uid="{FE689A42-CFD6-40FD-963B-3B7765442F4D}"/>
+    <hyperlink ref="D27" r:id="rId51" xr:uid="{0985532F-97C4-4537-AB76-C46128AE9E53}"/>
+    <hyperlink ref="D28" r:id="rId52" xr:uid="{EA2F34E1-F0AE-4FA5-AB4E-A09519C1AE95}"/>
+    <hyperlink ref="D29" r:id="rId53" xr:uid="{1A0E11DD-C9BD-4B8F-8857-531A124F7BA2}"/>
+    <hyperlink ref="D30" r:id="rId54" xr:uid="{097B9D40-C3E9-4997-965B-6E0E9DD7BB92}"/>
+    <hyperlink ref="D31" r:id="rId55" xr:uid="{A518BD5F-0F54-4C21-840A-1EE309D16392}"/>
+    <hyperlink ref="D32" r:id="rId56" xr:uid="{90C5C1E1-0789-4CF7-99DC-4080C6E46CCD}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Reports.xlsx
+++ b/data/Reports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\landscapingUOB-api\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F78EA7BE-A907-48F0-B81A-15CD6BBE5EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5FF44F-2907-4B90-A011-88D3CD122BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="275">
   <si>
     <t>Year</t>
   </si>
@@ -833,6 +833,18 @@
   </si>
   <si>
     <t>S39A Building</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Estimated Cost</t>
+  </si>
+  <si>
+    <t>Expected End Date</t>
+  </si>
+  <si>
+    <t>Start Date</t>
   </si>
 </sst>
 </file>
@@ -1320,7 +1332,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K57"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O57"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" style="17" customWidth="1"/>
@@ -1332,11 +1347,14 @@
     <col min="7" max="8" width="50" style="18" customWidth="1"/>
     <col min="9" max="10" width="12" style="18" customWidth="1"/>
     <col min="11" max="11" width="60" style="18" customWidth="1"/>
-    <col min="12" max="12" width="8.7265625" style="18" customWidth="1"/>
-    <col min="13" max="16384" width="8.7265625" style="18"/>
+    <col min="12" max="12" width="17.81640625" style="18" customWidth="1"/>
+    <col min="13" max="13" width="17.54296875" style="18" customWidth="1"/>
+    <col min="14" max="14" width="17.453125" style="18" customWidth="1"/>
+    <col min="15" max="15" width="17.7265625" style="18" customWidth="1"/>
+    <col min="16" max="16384" width="8.7265625" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" s="2" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1370,8 +1388,20 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L1" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>2024</v>
       </c>
@@ -1406,7 +1436,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>2024</v>
       </c>
@@ -1441,7 +1471,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="5" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" s="5" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>2024</v>
       </c>
@@ -1476,7 +1506,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>2024</v>
       </c>
@@ -1511,7 +1541,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>2024</v>
       </c>
@@ -1546,7 +1576,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>2024</v>
       </c>
@@ -1581,7 +1611,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>2024</v>
       </c>
@@ -1616,7 +1646,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>2024</v>
       </c>
@@ -1651,7 +1681,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>2024</v>
       </c>
@@ -1686,7 +1716,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>2024</v>
       </c>
@@ -1721,7 +1751,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>2024</v>
       </c>
@@ -1756,7 +1786,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:11" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>2024</v>
       </c>
@@ -1791,7 +1821,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:11" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>2024</v>
       </c>
@@ -1826,7 +1856,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>2024</v>
       </c>
@@ -1861,7 +1891,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>2024</v>
       </c>
@@ -2938,6 +2968,7 @@
     <hyperlink ref="D31" r:id="rId55" xr:uid="{A518BD5F-0F54-4C21-840A-1EE309D16392}"/>
     <hyperlink ref="D32" r:id="rId56" xr:uid="{90C5C1E1-0789-4CF7-99DC-4080C6E46CCD}"/>
   </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="8" scale="50" fitToHeight="0" orientation="landscape" r:id="rId57"/>
 </worksheet>
 </file>
--- a/data/Reports.xlsx
+++ b/data/Reports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\landscapingUOB-api\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5FF44F-2907-4B90-A011-88D3CD122BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096DEF2F-A5BF-4D57-B1D6-78AEA94E2ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="296">
   <si>
     <t>Year</t>
   </si>
@@ -845,6 +845,72 @@
   </si>
   <si>
     <t>Start Date</t>
+  </si>
+  <si>
+    <t>Previously: scattered, dry, and unhealthy random trees with invasive and dried weeds</t>
+  </si>
+  <si>
+    <t>After clearing the site and preparing the soil, 40 Delonix regia trees were planted. Planting beds were defined and landscaped with Sphagneticola trilobata as ground cover, bordered with Alternanthera. Seasonal Catharanthus roseus flowers and decorative cacti were also added</t>
+  </si>
+  <si>
+    <t>Site redevelopment and rehabilitation in line with modern landscaping standards to improve operational efficiency.</t>
+  </si>
+  <si>
+    <t>Landscaping was implemented across three levels:
+Upper level: a roundabout hedge of dwarf Bougainvillea.
+Middle level: a mixed-color Bougainvillea hedge.
+Lower level: ground cover using Alternanthera, enhanced with selected ornamental plants and cacti in the lower beds.</t>
+  </si>
+  <si>
+    <t>Site development and beautification in line with modern landscaping standards</t>
+  </si>
+  <si>
+    <t>The area was redesigned into defined planting beds and seating spaces. Landscaping included cacti, Ficus microcarpa (Ficus Panda), Cycas revoluta, dwarf Dracaena trifasciata varieties, with ground cover using Alternanthera and Sphagneticola trilobata</t>
+  </si>
+  <si>
+    <t>Trees were pruned and reshaped to eliminate overlap and improve safety. The area was cleared of debris, the landscaped area was expanded in an organized manner, and the overall streetscape aesthetics were enhanced.</t>
+  </si>
+  <si>
+    <t>All debris was removed, the soil was prepared and fertilized, and a new irrigation system was installed within the roundabout. A Albizia lebbeck tree was planted at the center, seasonal flowers were arranged along the curb edging, ornamental plants were added, and turf grass was installed as green ground cover</t>
+  </si>
+  <si>
+    <t>Following rehabilitation and site cleanup, Azadirachta indica trees were planted in an organized layout. Sand mounds were formed in selected areas, and various plants were introduced, including Thymus, Cymbopogon citratus, Bahraini basil, and mint. A curbside hedge of Bougainvillea was installed, with Sphagneticola trilobata used as ground cover</t>
+  </si>
+  <si>
+    <t>Planting beds were rehabilitated and upgraded in line with modern landscaping standards. Sustainable and ornamental species were introduced, including Tradescantia spathacea, Aloe vera, Agave, halfa grass, and Chlorophytum comosum, along with ground cover and ornamental trees to enhance the overall landscape</t>
+  </si>
+  <si>
+    <t>The soil and planting beds were rehabilitated, and ornamental trees were planted in an organized layout in line with modern landscaping standards</t>
+  </si>
+  <si>
+    <t>After soil preparation and installation of an irrigation system, ornamental trees and decorative plants were planted, seasonal flowers were added, and ground cover was installed to enhance the landscape</t>
+  </si>
+  <si>
+    <t>The land and soil were rehabilitated, ornamental trees were planted, and decorative plants and cacti were added within defined planting beds, along with appropriate ground cover to enhance the landscape</t>
+  </si>
+  <si>
+    <t>Previously: an old, woody, and deteriorated hedge of Volkameria inermis (wild jasmine).</t>
+  </si>
+  <si>
+    <t>Previously: mature Ficus microcarpa trees with degraded soil, invasive weeds, and agricultural debris.</t>
+  </si>
+  <si>
+    <t>Previously: overgrown and overlapping trees obstruct visibility and pose safety risks to pedestrians and drivers; some were dropping, woody, and visually appealing.</t>
+  </si>
+  <si>
+    <t>Previously: dry trees and invasive weeds negatively affecting the overall landscape appearance</t>
+  </si>
+  <si>
+    <t>Previously: randomly planted Conocarpus trees near the Ground Services Complex, with old woody and broken branches, invasive dry weeds, and agricultural debris across the site</t>
+  </si>
+  <si>
+    <t>Previously: scattered and dry trees, with old invasive weeds and debris within the planting areas</t>
+  </si>
+  <si>
+    <t>Previously: randomly planted Conocarpus trees with agricultural debris and invasive weeds on site</t>
+  </si>
+  <si>
+    <t>Western Gate Outer Roundabout</t>
   </si>
 </sst>
 </file>
@@ -953,7 +1019,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -990,14 +1056,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -1335,23 +1393,23 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8" style="17" customWidth="1"/>
-    <col min="2" max="2" width="12" style="17" customWidth="1"/>
-    <col min="3" max="3" width="37" style="18" customWidth="1"/>
-    <col min="4" max="4" width="45" style="18" customWidth="1"/>
-    <col min="5" max="5" width="40" style="18" customWidth="1"/>
-    <col min="6" max="6" width="12" style="18" customWidth="1"/>
-    <col min="7" max="8" width="50" style="18" customWidth="1"/>
-    <col min="9" max="10" width="12" style="18" customWidth="1"/>
-    <col min="11" max="11" width="60" style="18" customWidth="1"/>
-    <col min="12" max="12" width="17.81640625" style="18" customWidth="1"/>
-    <col min="13" max="13" width="17.54296875" style="18" customWidth="1"/>
-    <col min="14" max="14" width="17.453125" style="18" customWidth="1"/>
-    <col min="15" max="15" width="17.7265625" style="18" customWidth="1"/>
-    <col min="16" max="16384" width="8.7265625" style="18"/>
+    <col min="1" max="1" width="8" style="13" customWidth="1"/>
+    <col min="2" max="2" width="12" style="13" customWidth="1"/>
+    <col min="3" max="3" width="37" style="14" customWidth="1"/>
+    <col min="4" max="4" width="45" style="14" customWidth="1"/>
+    <col min="5" max="5" width="40" style="14" customWidth="1"/>
+    <col min="6" max="6" width="12" style="14" customWidth="1"/>
+    <col min="7" max="8" width="50" style="14" customWidth="1"/>
+    <col min="9" max="10" width="12" style="14" customWidth="1"/>
+    <col min="11" max="11" width="60" style="14" customWidth="1"/>
+    <col min="12" max="12" width="17.81640625" style="14" customWidth="1"/>
+    <col min="13" max="13" width="17.54296875" style="14" customWidth="1"/>
+    <col min="14" max="14" width="17.453125" style="14" customWidth="1"/>
+    <col min="15" max="15" width="17.7265625" style="14" customWidth="1"/>
+    <col min="16" max="16384" width="8.7265625" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="2" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
@@ -1411,7 +1469,7 @@
       <c r="C2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="22" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="4" t="s">
@@ -1446,7 +1504,7 @@
       <c r="C3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="22" t="s">
         <v>19</v>
       </c>
       <c r="E3" s="4" t="s">
@@ -1481,7 +1539,7 @@
       <c r="C4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="22" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="4" t="s">
@@ -1516,7 +1574,7 @@
       <c r="C5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="22" t="s">
         <v>33</v>
       </c>
       <c r="E5" s="4" t="s">
@@ -1551,7 +1609,7 @@
       <c r="C6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="22" t="s">
         <v>39</v>
       </c>
       <c r="E6" s="4" t="s">
@@ -1586,7 +1644,7 @@
       <c r="C7" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="22" t="s">
         <v>47</v>
       </c>
       <c r="E7" s="4" t="s">
@@ -1621,7 +1679,7 @@
       <c r="C8" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="22" t="s">
         <v>54</v>
       </c>
       <c r="E8" s="4" t="s">
@@ -1656,7 +1714,7 @@
       <c r="C9" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="22" t="s">
         <v>61</v>
       </c>
       <c r="E9" s="4" t="s">
@@ -1691,7 +1749,7 @@
       <c r="C10" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="22" t="s">
         <v>67</v>
       </c>
       <c r="E10" s="4" t="s">
@@ -1726,7 +1784,7 @@
       <c r="C11" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="22" t="s">
         <v>73</v>
       </c>
       <c r="E11" s="4" t="s">
@@ -1761,7 +1819,7 @@
       <c r="C12" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="22" t="s">
         <v>80</v>
       </c>
       <c r="E12" s="4" t="s">
@@ -1796,7 +1854,7 @@
       <c r="C13" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="D13" s="22" t="s">
         <v>87</v>
       </c>
       <c r="E13" s="4" t="s">
@@ -1831,7 +1889,7 @@
       <c r="C14" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="22" t="s">
         <v>95</v>
       </c>
       <c r="E14" s="4" t="s">
@@ -1866,7 +1924,7 @@
       <c r="C15" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="22" t="s">
         <v>102</v>
       </c>
       <c r="E15" s="4" t="s">
@@ -1901,7 +1959,7 @@
       <c r="C16" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="22" t="s">
         <v>107</v>
       </c>
       <c r="E16" s="4" t="s">
@@ -1936,7 +1994,7 @@
       <c r="C17" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D17" s="22" t="s">
         <v>114</v>
       </c>
       <c r="E17" s="4" t="s">
@@ -1971,7 +2029,7 @@
       <c r="C18" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="22" t="s">
         <v>121</v>
       </c>
       <c r="E18" s="4" t="s">
@@ -2006,7 +2064,7 @@
       <c r="C19" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="D19" s="22" t="s">
         <v>126</v>
       </c>
       <c r="E19" s="4" t="s">
@@ -2041,7 +2099,7 @@
       <c r="C20" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="22" t="s">
         <v>133</v>
       </c>
       <c r="E20" s="4" t="s">
@@ -2076,7 +2134,7 @@
       <c r="C21" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="D21" s="22" t="s">
         <v>139</v>
       </c>
       <c r="E21" s="4" t="s">
@@ -2111,7 +2169,7 @@
       <c r="C22" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="D22" s="26" t="s">
+      <c r="D22" s="22" t="s">
         <v>145</v>
       </c>
       <c r="E22" s="4" t="s">
@@ -2146,7 +2204,7 @@
       <c r="C23" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="D23" s="26" t="s">
+      <c r="D23" s="22" t="s">
         <v>149</v>
       </c>
       <c r="E23" s="4" t="s">
@@ -2181,7 +2239,7 @@
       <c r="C24" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D24" s="26" t="s">
+      <c r="D24" s="22" t="s">
         <v>153</v>
       </c>
       <c r="E24" s="4" t="s">
@@ -2216,7 +2274,7 @@
       <c r="C25" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="D25" s="25" t="s">
+      <c r="D25" s="21" t="s">
         <v>159</v>
       </c>
       <c r="E25" s="7" t="s">
@@ -2251,7 +2309,7 @@
       <c r="C26" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="D26" s="25" t="s">
+      <c r="D26" s="21" t="s">
         <v>166</v>
       </c>
       <c r="E26" s="7" t="s">
@@ -2286,7 +2344,7 @@
       <c r="C27" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="D27" s="25" t="s">
+      <c r="D27" s="21" t="s">
         <v>173</v>
       </c>
       <c r="E27" s="7" t="s">
@@ -2321,7 +2379,7 @@
       <c r="C28" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="D28" s="25" t="s">
+      <c r="D28" s="21" t="s">
         <v>180</v>
       </c>
       <c r="E28" s="7" t="s">
@@ -2356,7 +2414,7 @@
       <c r="C29" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="D29" s="25" t="s">
+      <c r="D29" s="21" t="s">
         <v>186</v>
       </c>
       <c r="E29" s="7" t="s">
@@ -2391,7 +2449,7 @@
       <c r="C30" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="D30" s="25" t="s">
+      <c r="D30" s="21" t="s">
         <v>193</v>
       </c>
       <c r="E30" s="7" t="s">
@@ -2426,7 +2484,7 @@
       <c r="C31" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="D31" s="25" t="s">
+      <c r="D31" s="21" t="s">
         <v>199</v>
       </c>
       <c r="E31" s="7" t="s">
@@ -2461,7 +2519,7 @@
       <c r="C32" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D32" s="25" t="s">
+      <c r="D32" s="21" t="s">
         <v>206</v>
       </c>
       <c r="E32" s="7" t="s">
@@ -2496,7 +2554,7 @@
       <c r="C33" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D33" s="25" t="s">
+      <c r="D33" s="21" t="s">
         <v>212</v>
       </c>
       <c r="E33" s="7" t="s">
@@ -2531,7 +2589,7 @@
       <c r="C34" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="D34" s="25" t="s">
+      <c r="D34" s="21" t="s">
         <v>217</v>
       </c>
       <c r="E34" s="7" t="s">
@@ -2566,7 +2624,7 @@
       <c r="C35" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="D35" s="25" t="s">
+      <c r="D35" s="21" t="s">
         <v>224</v>
       </c>
       <c r="E35" s="7" t="s">
@@ -2591,7 +2649,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="36" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" s="12" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A36" s="9">
         <v>2026</v>
       </c>
@@ -2604,9 +2662,17 @@
       <c r="D36" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="E36" s="10"/>
-    </row>
-    <row r="37" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="E36" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" s="12" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A37" s="9">
         <v>2026</v>
       </c>
@@ -2619,9 +2685,17 @@
       <c r="D37" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="E37" s="10"/>
-    </row>
-    <row r="38" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="E37" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" s="12" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A38" s="9">
         <v>2026</v>
       </c>
@@ -2635,8 +2709,14 @@
         <v>240</v>
       </c>
       <c r="E38" s="10"/>
-    </row>
-    <row r="39" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="G38" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A39" s="9">
         <v>2026</v>
       </c>
@@ -2650,23 +2730,35 @@
         <v>244</v>
       </c>
       <c r="E39" s="10"/>
-    </row>
-    <row r="40" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="13">
+      <c r="G39" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="H39" s="12" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" s="12" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="A40" s="9">
         <v>2026</v>
       </c>
       <c r="B40" s="9">
         <v>5</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C40" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D40" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="E40" s="14"/>
-    </row>
-    <row r="41" spans="1:11" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="E40" s="10"/>
+      <c r="G40" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="H40" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" s="12" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A41" s="9">
         <v>2026</v>
       </c>
@@ -2680,8 +2772,14 @@
         <v>247</v>
       </c>
       <c r="E41" s="10"/>
-    </row>
-    <row r="42" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="G41" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="H41" s="12" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" s="12" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A42" s="9">
         <v>2026</v>
       </c>
@@ -2695,8 +2793,14 @@
         <v>248</v>
       </c>
       <c r="E42" s="10"/>
-    </row>
-    <row r="43" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="G42" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A43" s="9">
         <v>2026</v>
       </c>
@@ -2706,12 +2810,18 @@
       <c r="C43" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="D43" s="23" t="s">
+      <c r="D43" s="19" t="s">
         <v>264</v>
       </c>
       <c r="E43" s="10"/>
-    </row>
-    <row r="44" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="G43" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="H43" s="12" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A44" s="9">
         <v>2026</v>
       </c>
@@ -2721,12 +2831,18 @@
       <c r="C44" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="D44" s="23" t="s">
+      <c r="D44" s="19" t="s">
         <v>266</v>
       </c>
       <c r="E44" s="10"/>
-    </row>
-    <row r="45" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="G44" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="H44" s="12" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A45" s="9">
         <v>2026</v>
       </c>
@@ -2736,176 +2852,195 @@
       <c r="C45" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="D45" s="23" t="s">
+      <c r="D45" s="19" t="s">
         <v>224</v>
       </c>
       <c r="E45" s="10"/>
-    </row>
-    <row r="46" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="19">
+      <c r="G45" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="H45" s="12" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B46" s="9">
+        <v>11</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="D46" s="19"/>
+      <c r="E46" s="10"/>
+    </row>
+    <row r="47" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="15">
         <v>2027</v>
       </c>
-      <c r="B46" s="19">
+      <c r="B47" s="15">
         <v>1</v>
       </c>
-      <c r="C46" s="20" t="s">
+      <c r="C47" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="D46" s="21" t="s">
+      <c r="D47" s="17" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="47" spans="1:11" s="22" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A47" s="19">
+    <row r="48" spans="1:11" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A48" s="15">
         <v>2027</v>
       </c>
-      <c r="B47" s="19">
+      <c r="B48" s="15">
         <v>2</v>
       </c>
-      <c r="C47" s="20" t="s">
+      <c r="C48" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="D47" s="21" t="s">
+      <c r="D48" s="17" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="48" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="19">
+    <row r="49" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="15">
         <v>2027</v>
       </c>
-      <c r="B48" s="19">
+      <c r="B49" s="15">
         <v>3</v>
       </c>
-      <c r="C48" s="20" t="s">
+      <c r="C49" s="16" t="s">
         <v>233</v>
       </c>
-      <c r="D48" s="21" t="s">
+      <c r="D49" s="17" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="49" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="19">
+    <row r="50" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="15">
         <v>2027</v>
       </c>
-      <c r="B49" s="19">
+      <c r="B50" s="15">
         <v>4</v>
       </c>
-      <c r="C49" s="20" t="s">
+      <c r="C50" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="D49" s="21" t="s">
+      <c r="D50" s="17" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="50" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="19">
+    <row r="51" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="15">
         <v>2027</v>
       </c>
-      <c r="B50" s="19">
+      <c r="B51" s="15">
         <v>5</v>
       </c>
-      <c r="C50" s="20" t="s">
+      <c r="C51" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="D50" s="21" t="s">
+      <c r="D51" s="17" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="51" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="19">
+    <row r="52" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="15">
         <v>2027</v>
       </c>
-      <c r="B51" s="19">
+      <c r="B52" s="15">
         <v>6</v>
       </c>
-      <c r="C51" s="20" t="s">
+      <c r="C52" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="D51" s="21" t="s">
+      <c r="D52" s="17" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="52" spans="1:4" s="22" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A52" s="19">
+    <row r="53" spans="1:4" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A53" s="15">
         <v>2027</v>
       </c>
-      <c r="B52" s="19">
+      <c r="B53" s="15">
         <v>7</v>
       </c>
-      <c r="C52" s="20" t="s">
+      <c r="C53" s="16" t="s">
         <v>236</v>
       </c>
-      <c r="D52" s="21" t="s">
+      <c r="D53" s="17" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="53" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="19">
+    <row r="54" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="15">
         <v>2027</v>
       </c>
-      <c r="B53" s="19">
+      <c r="B54" s="15">
         <v>8</v>
       </c>
-      <c r="C53" s="20" t="s">
+      <c r="C54" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="D53" s="21" t="s">
+      <c r="D54" s="17" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="54" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="19">
+    <row r="55" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="15">
         <v>2027</v>
       </c>
-      <c r="B54" s="19">
+      <c r="B55" s="15">
         <v>9</v>
       </c>
-      <c r="C54" s="22" t="s">
+      <c r="C55" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="D54" s="24" t="s">
+      <c r="D55" s="20" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="55" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="19">
+    <row r="56" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="15">
         <v>2027</v>
       </c>
-      <c r="B55" s="19">
+      <c r="B56" s="15">
         <v>10</v>
       </c>
-      <c r="C55" s="22" t="s">
+      <c r="C56" s="18" t="s">
         <v>258</v>
       </c>
-      <c r="D55" s="24" t="s">
+      <c r="D56" s="20" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="56" spans="1:4" s="22" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A56" s="19">
+    <row r="57" spans="1:4" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A57" s="15">
         <v>2027</v>
       </c>
-      <c r="B56" s="19">
+      <c r="B57" s="15">
         <v>11</v>
       </c>
-      <c r="C56" s="22" t="s">
+      <c r="C57" s="18" t="s">
         <v>259</v>
       </c>
-      <c r="D56" s="24" t="s">
+      <c r="D57" s="20" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="57" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="19">
+    <row r="58" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="15">
         <v>2027</v>
       </c>
-      <c r="B57" s="19">
+      <c r="B58" s="15">
         <v>12</v>
       </c>
-      <c r="C57" s="22" t="s">
+      <c r="C58" s="18" t="s">
         <v>260</v>
       </c>
-      <c r="D57" s="24" t="s">
+      <c r="D58" s="20" t="s">
         <v>269</v>
       </c>
     </row>
@@ -2914,24 +3049,24 @@
     <hyperlink ref="D36" r:id="rId1" xr:uid="{1000462C-B238-431A-B2A1-3FC2BD2E2813}"/>
     <hyperlink ref="D37" r:id="rId2" xr:uid="{1B9305A2-EFAE-494D-AE61-72B82236A00A}"/>
     <hyperlink ref="D38" r:id="rId3" xr:uid="{37366389-41FF-4E4B-BBAA-23F6E2BDE2E5}"/>
-    <hyperlink ref="D47" r:id="rId4" xr:uid="{0D35B99D-C761-48D2-A6FC-1AA9DABC570E}"/>
-    <hyperlink ref="D48" r:id="rId5" xr:uid="{2C3EF60F-AF56-486A-A65A-90521D1BE076}"/>
+    <hyperlink ref="D48" r:id="rId4" xr:uid="{0D35B99D-C761-48D2-A6FC-1AA9DABC570E}"/>
+    <hyperlink ref="D49" r:id="rId5" xr:uid="{2C3EF60F-AF56-486A-A65A-90521D1BE076}"/>
     <hyperlink ref="D39" r:id="rId6" xr:uid="{C95DBB32-C8B9-4192-B5A8-A2BBC5AE8709}"/>
-    <hyperlink ref="D49" r:id="rId7" xr:uid="{0245B09C-A05C-42F8-9F53-B3C0DF8A3B3B}"/>
+    <hyperlink ref="D50" r:id="rId7" xr:uid="{0245B09C-A05C-42F8-9F53-B3C0DF8A3B3B}"/>
     <hyperlink ref="D40" r:id="rId8" xr:uid="{41838A62-16DE-40C3-A6D6-65FCB68C828C}"/>
     <hyperlink ref="D41" r:id="rId9" xr:uid="{1DA3C22A-9C35-431D-9E54-09A3B7395A7F}"/>
     <hyperlink ref="D42" r:id="rId10" xr:uid="{D058C4E8-F8D4-42F8-A17C-BC9F6C69C57E}"/>
-    <hyperlink ref="D50" r:id="rId11" xr:uid="{D2DB956F-0AE2-4C2E-8230-86EBD2EFD849}"/>
-    <hyperlink ref="D51" r:id="rId12" xr:uid="{7FDA2993-EE4C-4AEE-A744-BD17EE8DF685}"/>
-    <hyperlink ref="D52" r:id="rId13" xr:uid="{C3597594-CEFA-42FD-809C-D15002498BB3}"/>
-    <hyperlink ref="D53" r:id="rId14" xr:uid="{D97DA6E9-7A4E-4C31-A094-581BEFAE38C5}"/>
-    <hyperlink ref="D46" r:id="rId15" xr:uid="{66A90A50-7813-4BE2-835B-908012476FD3}"/>
+    <hyperlink ref="D51" r:id="rId11" xr:uid="{D2DB956F-0AE2-4C2E-8230-86EBD2EFD849}"/>
+    <hyperlink ref="D52" r:id="rId12" xr:uid="{7FDA2993-EE4C-4AEE-A744-BD17EE8DF685}"/>
+    <hyperlink ref="D53" r:id="rId13" xr:uid="{C3597594-CEFA-42FD-809C-D15002498BB3}"/>
+    <hyperlink ref="D54" r:id="rId14" xr:uid="{D97DA6E9-7A4E-4C31-A094-581BEFAE38C5}"/>
+    <hyperlink ref="D47" r:id="rId15" xr:uid="{66A90A50-7813-4BE2-835B-908012476FD3}"/>
     <hyperlink ref="D43" r:id="rId16" xr:uid="{147ACBB0-7330-4375-A5F5-59953D8672C7}"/>
-    <hyperlink ref="D54" r:id="rId17" xr:uid="{BFA2C4D2-299F-48F3-8C92-FA17876C33A6}"/>
+    <hyperlink ref="D55" r:id="rId17" xr:uid="{BFA2C4D2-299F-48F3-8C92-FA17876C33A6}"/>
     <hyperlink ref="D44" r:id="rId18" xr:uid="{89B226A2-CD02-441A-9332-0B81D06E4B1B}"/>
-    <hyperlink ref="D55" r:id="rId19" xr:uid="{0455FD2A-FBB6-4033-952F-93501D724B92}"/>
-    <hyperlink ref="D56" r:id="rId20" xr:uid="{6900060F-FF2A-4358-B515-6B63FC613431}"/>
-    <hyperlink ref="D57" r:id="rId21" xr:uid="{57F6A3F4-C756-45F7-BF88-FF8069986A7A}"/>
+    <hyperlink ref="D56" r:id="rId19" xr:uid="{0455FD2A-FBB6-4033-952F-93501D724B92}"/>
+    <hyperlink ref="D57" r:id="rId20" xr:uid="{6900060F-FF2A-4358-B515-6B63FC613431}"/>
+    <hyperlink ref="D58" r:id="rId21" xr:uid="{57F6A3F4-C756-45F7-BF88-FF8069986A7A}"/>
     <hyperlink ref="D35" r:id="rId22" xr:uid="{D5D38438-E4B6-481E-8C69-DFDC27DE2CD2}"/>
     <hyperlink ref="D45" r:id="rId23" xr:uid="{A775D76D-67D0-401B-BFFA-3EBAA24D153A}"/>
     <hyperlink ref="D34" r:id="rId24" xr:uid="{A2DE1ABB-0FFA-4088-A49E-6A441A99A49F}"/>

--- a/data/Reports.xlsx
+++ b/data/Reports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\landscapingUOB-api\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096DEF2F-A5BF-4D57-B1D6-78AEA94E2ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F5DA44-22E8-4567-A3CC-1B38315B5D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="294">
   <si>
     <t>Year</t>
   </si>
@@ -613,9 +613,6 @@
     <t>Sustainable ornamental trees were planted</t>
   </si>
   <si>
-    <t>Enhanced the overall appearance of the site and added an aesthetic character; rehabilitated an area of approximately 160 RM and planted 50 ornamental trees.</t>
-  </si>
-  <si>
     <t>Open courtyard behind the main mosque</t>
   </si>
   <si>
@@ -634,9 +631,6 @@
     <t>1,000 sustainable ornamental trees were planted</t>
   </si>
   <si>
-    <t>Rehabilitated an area of approximately 10,800 m², including the removal of weeds, waste, and old soil, replacement with new agricultural sand, installation of an irrigation network, and planting of sustainable trees with landscape design.</t>
-  </si>
-  <si>
     <t>Student rest areas of the College of Science and the College of Information Technology</t>
   </si>
   <si>
@@ -652,12 +646,6 @@
     <t>Previously: neglected area with harmful old trees, weeds, and waste</t>
   </si>
   <si>
-    <t>The area was rehabilitated with sustainable ornamental trees, various plants, and seasonal flowers.</t>
-  </si>
-  <si>
-    <t>The project includes removing harmful trees, preparing basins and soil, and implementing landscape designs. The second phase includes planting more than 100 sustainable shade trees and increasing plant cover with new species.</t>
-  </si>
-  <si>
     <t>https://maps.app.goo.gl/fqocRyHqpnybUmdBA</t>
   </si>
   <si>
@@ -667,9 +655,6 @@
     <t>The entire area was planted and landscaped to match the environment and the general aesthetic appearance.</t>
   </si>
   <si>
-    <t>Developed the area to make it more attractive for visitors, students, and staff.</t>
-  </si>
-  <si>
     <t>Opposite the Student Affairs parking lot (S38)</t>
   </si>
   <si>
@@ -688,9 +673,6 @@
     <t>100 Bahraini almond trees were planted</t>
   </si>
   <si>
-    <t>Rehabilitation of a 1,100 m² area is in progress. The space will be afforested with 100 Bahraini almond trees in collaboration with the College of Health Sciences, the College of Physical Education, and a group of students participating in the tree planting.</t>
-  </si>
-  <si>
     <t>S20 Building</t>
   </si>
   <si>
@@ -700,12 +682,6 @@
     <t>960 m²</t>
   </si>
   <si>
-    <t>The area will be replanted with sustainable shade trees, ornamental plants, and seasonal flowers, adding distinctive landscaping that enhances visual appeal and promotes vegetation sustainability.</t>
-  </si>
-  <si>
-    <t>Ongoing project for removing harmful trees, preparing basins and soil, and implementing landscape design works.</t>
-  </si>
-  <si>
     <t>Flag Roundabout - Fountain</t>
   </si>
   <si>
@@ -853,64 +829,82 @@
     <t>After clearing the site and preparing the soil, 40 Delonix regia trees were planted. Planting beds were defined and landscaped with Sphagneticola trilobata as ground cover, bordered with Alternanthera. Seasonal Catharanthus roseus flowers and decorative cacti were also added</t>
   </si>
   <si>
-    <t>Site redevelopment and rehabilitation in line with modern landscaping standards to improve operational efficiency.</t>
+    <t>The area was redesigned into defined planting beds and seating spaces. Landscaping included cacti, Ficus microcarpa (Ficus Panda), Cycas revoluta, dwarf Dracaena trifasciata varieties, with ground cover using Alternanthera and Sphagneticola trilobata</t>
+  </si>
+  <si>
+    <t>All debris was removed, the soil was prepared and fertilized, and a new irrigation system was installed within the roundabout. A Albizia lebbeck tree was planted at the center, seasonal flowers were arranged along the curb edging, ornamental plants were added, and turf grass was installed as green ground cover</t>
+  </si>
+  <si>
+    <t>Following rehabilitation and site cleanup, Azadirachta indica trees were planted in an organized layout. Sand mounds were formed in selected areas, and various plants were introduced, including Thymus, Cymbopogon citratus, Bahraini basil, and mint. A curbside hedge of Bougainvillea was installed, with Sphagneticola trilobata used as ground cover</t>
+  </si>
+  <si>
+    <t>Planting beds were rehabilitated and upgraded in line with modern landscaping standards. Sustainable and ornamental species were introduced, including Tradescantia spathacea, Aloe vera, Agave, halfa grass, and Chlorophytum comosum, along with ground cover and ornamental trees to enhance the overall landscape</t>
+  </si>
+  <si>
+    <t>The soil and planting beds were rehabilitated, and ornamental trees were planted in an organized layout in line with modern landscaping standards</t>
+  </si>
+  <si>
+    <t>After soil preparation and installation of an irrigation system, ornamental trees and decorative plants were planted, seasonal flowers were added, and ground cover was installed to enhance the landscape</t>
+  </si>
+  <si>
+    <t>The land and soil were rehabilitated, ornamental trees were planted, and decorative plants and cacti were added within defined planting beds, along with appropriate ground cover to enhance the landscape</t>
+  </si>
+  <si>
+    <t>Previously: dry trees and invasive weeds negatively affecting the overall landscape appearance</t>
+  </si>
+  <si>
+    <t>Previously: randomly planted Conocarpus trees near the Ground Services Complex, with old woody and broken branches, invasive dry weeds, and agricultural debris across the site</t>
+  </si>
+  <si>
+    <t>Previously: scattered and dry trees, with old invasive weeds and debris within the planting areas</t>
+  </si>
+  <si>
+    <t>Previously: randomly planted Conocarpus trees with agricultural debris and invasive weeds on site</t>
+  </si>
+  <si>
+    <t>Western Gate Outer Roundabout</t>
+  </si>
+  <si>
+    <t>Previously: an old, woody, and deteriorated hedge of Volkameria inermis (wild jasmine)</t>
+  </si>
+  <si>
+    <t>Previously: mature Ficus microcarpa trees with degraded soil, invasive weeds, and agricultural debris</t>
+  </si>
+  <si>
+    <t>Previously: overgrown and overlapping trees obstruct visibility and pose safety risks to pedestrians and drivers; some were dropping, woody, and visually appealing</t>
+  </si>
+  <si>
+    <t>Trees were pruned and reshaped to eliminate overlap and improve safety. The area was cleared of debris, the landscaped area was expanded in an organized manner, and the overall streetscape aesthetics were enhanced</t>
   </si>
   <si>
     <t>Landscaping was implemented across three levels:
 Upper level: a roundabout hedge of dwarf Bougainvillea.
 Middle level: a mixed-color Bougainvillea hedge.
-Lower level: ground cover using Alternanthera, enhanced with selected ornamental plants and cacti in the lower beds.</t>
-  </si>
-  <si>
-    <t>Site development and beautification in line with modern landscaping standards</t>
-  </si>
-  <si>
-    <t>The area was redesigned into defined planting beds and seating spaces. Landscaping included cacti, Ficus microcarpa (Ficus Panda), Cycas revoluta, dwarf Dracaena trifasciata varieties, with ground cover using Alternanthera and Sphagneticola trilobata</t>
-  </si>
-  <si>
-    <t>Trees were pruned and reshaped to eliminate overlap and improve safety. The area was cleared of debris, the landscaped area was expanded in an organized manner, and the overall streetscape aesthetics were enhanced.</t>
-  </si>
-  <si>
-    <t>All debris was removed, the soil was prepared and fertilized, and a new irrigation system was installed within the roundabout. A Albizia lebbeck tree was planted at the center, seasonal flowers were arranged along the curb edging, ornamental plants were added, and turf grass was installed as green ground cover</t>
-  </si>
-  <si>
-    <t>Following rehabilitation and site cleanup, Azadirachta indica trees were planted in an organized layout. Sand mounds were formed in selected areas, and various plants were introduced, including Thymus, Cymbopogon citratus, Bahraini basil, and mint. A curbside hedge of Bougainvillea was installed, with Sphagneticola trilobata used as ground cover</t>
-  </si>
-  <si>
-    <t>Planting beds were rehabilitated and upgraded in line with modern landscaping standards. Sustainable and ornamental species were introduced, including Tradescantia spathacea, Aloe vera, Agave, halfa grass, and Chlorophytum comosum, along with ground cover and ornamental trees to enhance the overall landscape</t>
-  </si>
-  <si>
-    <t>The soil and planting beds were rehabilitated, and ornamental trees were planted in an organized layout in line with modern landscaping standards</t>
-  </si>
-  <si>
-    <t>After soil preparation and installation of an irrigation system, ornamental trees and decorative plants were planted, seasonal flowers were added, and ground cover was installed to enhance the landscape</t>
-  </si>
-  <si>
-    <t>The land and soil were rehabilitated, ornamental trees were planted, and decorative plants and cacti were added within defined planting beds, along with appropriate ground cover to enhance the landscape</t>
-  </si>
-  <si>
-    <t>Previously: an old, woody, and deteriorated hedge of Volkameria inermis (wild jasmine).</t>
-  </si>
-  <si>
-    <t>Previously: mature Ficus microcarpa trees with degraded soil, invasive weeds, and agricultural debris.</t>
-  </si>
-  <si>
-    <t>Previously: overgrown and overlapping trees obstruct visibility and pose safety risks to pedestrians and drivers; some were dropping, woody, and visually appealing.</t>
-  </si>
-  <si>
-    <t>Previously: dry trees and invasive weeds negatively affecting the overall landscape appearance</t>
-  </si>
-  <si>
-    <t>Previously: randomly planted Conocarpus trees near the Ground Services Complex, with old woody and broken branches, invasive dry weeds, and agricultural debris across the site</t>
-  </si>
-  <si>
-    <t>Previously: scattered and dry trees, with old invasive weeds and debris within the planting areas</t>
-  </si>
-  <si>
-    <t>Previously: randomly planted Conocarpus trees with agricultural debris and invasive weeds on site</t>
-  </si>
-  <si>
-    <t>Western Gate Outer Roundabout</t>
+Lower level: ground cover using Alternanthera, enhanced with selected ornamental plants and cacti in the lower beds</t>
+  </si>
+  <si>
+    <t>The area will be replanted with sustainable shade trees, ornamental plants, and seasonal flowers, adding distinctive landscaping that enhances visual appeal and promotes vegetation sustainability</t>
+  </si>
+  <si>
+    <t>The area was rehabilitated with sustainable ornamental trees, various plants, and seasonal flowers</t>
+  </si>
+  <si>
+    <t>Ongoing project for removing harmful trees, preparing basins and soil, and implementing landscape design works</t>
+  </si>
+  <si>
+    <t>Rehabilitation of a 1,100 m² area is in progress. The space will be afforested with 100 Bahraini almond trees in collaboration with the College of Health Sciences, the College of Physical Education, and a group of students participating in the tree planting</t>
+  </si>
+  <si>
+    <t>Developed the area to make it more attractive for visitors, students, and staff</t>
+  </si>
+  <si>
+    <t>The project includes removing harmful trees, preparing basins and soil, and implementing landscape designs. The second phase includes planting more than 100 sustainable shade trees and increasing plant cover with new species</t>
+  </si>
+  <si>
+    <t>Rehabilitated an area of approximately 10,800 m², including the removal of weeds, waste, and old soil, replacement with new agricultural sand, installation of an irrigation network, and planting of sustainable trees with landscape design</t>
+  </si>
+  <si>
+    <t>Enhanced the overall appearance of the site and added an aesthetic character; rehabilitated an area of approximately 160 RM and planted 50 ornamental trees</t>
   </si>
 </sst>
 </file>
@@ -1447,16 +1441,16 @@
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:15" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
@@ -2471,7 +2465,7 @@
         <v>50</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>197</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="8" customFormat="1" ht="58" x14ac:dyDescent="0.35">
@@ -2482,22 +2476,22 @@
         <v>7</v>
       </c>
       <c r="C31" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="D31" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="D31" s="21" t="s">
+      <c r="E31" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="F31" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="G31" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="H31" s="7" t="s">
         <v>202</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>203</v>
       </c>
       <c r="I31" s="7" t="s">
         <v>21</v>
@@ -2506,7 +2500,7 @@
         <v>1000</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>204</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="8" customFormat="1" ht="58" x14ac:dyDescent="0.35">
@@ -2517,22 +2511,22 @@
         <v>8</v>
       </c>
       <c r="C32" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="E32" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="F32" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="G32" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="F32" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>209</v>
-      </c>
       <c r="H32" s="7" t="s">
-        <v>210</v>
+        <v>287</v>
       </c>
       <c r="I32" s="7" t="s">
         <v>21</v>
@@ -2541,7 +2535,7 @@
         <v>104</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>211</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" spans="1:11" s="8" customFormat="1" ht="29" x14ac:dyDescent="0.35">
@@ -2555,10 +2549,10 @@
         <v>106</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>109</v>
@@ -2567,7 +2561,7 @@
         <v>110</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I33" s="7" t="s">
         <v>109</v>
@@ -2576,7 +2570,7 @@
         <v>12</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>215</v>
+        <v>290</v>
       </c>
     </row>
     <row r="34" spans="1:11" s="8" customFormat="1" ht="58" x14ac:dyDescent="0.35">
@@ -2587,22 +2581,22 @@
         <v>10</v>
       </c>
       <c r="C34" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="H34" s="7" t="s">
         <v>216</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>221</v>
       </c>
       <c r="I34" s="7" t="s">
         <v>21</v>
@@ -2611,7 +2605,7 @@
         <v>100</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>222</v>
+        <v>289</v>
       </c>
     </row>
     <row r="35" spans="1:11" s="8" customFormat="1" ht="58" x14ac:dyDescent="0.35">
@@ -2622,22 +2616,22 @@
         <v>11</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>226</v>
+        <v>286</v>
       </c>
       <c r="I35" s="7" t="s">
         <v>21</v>
@@ -2646,7 +2640,7 @@
         <v>21</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>227</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" spans="1:11" s="12" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
@@ -2657,19 +2651,17 @@
         <v>1</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>277</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="E36" s="10"/>
       <c r="G36" s="12" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
     </row>
     <row r="37" spans="1:11" s="12" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
@@ -2680,19 +2672,17 @@
         <v>2</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>279</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="E37" s="10"/>
       <c r="G37" s="12" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="12" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
@@ -2703,17 +2693,17 @@
         <v>3</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
     </row>
     <row r="39" spans="1:11" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
@@ -2724,17 +2714,17 @@
         <v>4</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="E39" s="10"/>
       <c r="G39" s="12" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="40" spans="1:11" s="12" customFormat="1" ht="87" x14ac:dyDescent="0.35">
@@ -2745,17 +2735,17 @@
         <v>5</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="E40" s="10"/>
       <c r="G40" s="12" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="12" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
@@ -2766,17 +2756,17 @@
         <v>6</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="E41" s="10"/>
       <c r="G41" s="12" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="12" customFormat="1" ht="87" x14ac:dyDescent="0.35">
@@ -2787,17 +2777,17 @@
         <v>7</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="E42" s="10"/>
       <c r="G42" s="12" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
@@ -2808,17 +2798,17 @@
         <v>8</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="E43" s="10"/>
       <c r="G43" s="12" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
     </row>
     <row r="44" spans="1:11" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
@@ -2829,17 +2819,17 @@
         <v>9</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="E44" s="10"/>
       <c r="G44" s="12" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="45" spans="1:11" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
@@ -2850,17 +2840,17 @@
         <v>10</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E45" s="10"/>
       <c r="G45" s="12" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
@@ -2871,7 +2861,7 @@
         <v>11</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="D46" s="19"/>
       <c r="E46" s="10"/>
@@ -2884,10 +2874,10 @@
         <v>1</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="48" spans="1:11" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
@@ -2898,10 +2888,10 @@
         <v>2</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.35">
@@ -2912,10 +2902,10 @@
         <v>3</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.35">
@@ -2926,10 +2916,10 @@
         <v>4</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.35">
@@ -2940,10 +2930,10 @@
         <v>5</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.35">
@@ -2954,10 +2944,10 @@
         <v>6</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
@@ -2968,10 +2958,10 @@
         <v>7</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.35">
@@ -2982,10 +2972,10 @@
         <v>8</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.35">
@@ -2996,10 +2986,10 @@
         <v>9</v>
       </c>
       <c r="C55" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="D55" s="20" t="s">
         <v>257</v>
-      </c>
-      <c r="D55" s="20" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.35">
@@ -3010,10 +3000,10 @@
         <v>10</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="D56" s="20" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
@@ -3024,10 +3014,10 @@
         <v>11</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="D57" s="20" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.35">
@@ -3038,10 +3028,10 @@
         <v>12</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="D58" s="20" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
